--- a/data/trans_dic/P1806_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1806_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses han visitado un podólogo</t>
+          <t>Población según si en los últimos 12 meses han visitado un podólogo (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,37</t>
+          <t>0,48; 5,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,67</t>
+          <t>1,4; 7,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,75</t>
+          <t>1,26; 4,84</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,78</t>
+          <t>0,59; 4,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,72</t>
+          <t>0,83; 3,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,42</t>
+          <t>0,95; 3,11</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,74</t>
+          <t>1,08; 3,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,26</t>
+          <t>1,8; 4,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,45</t>
+          <t>1,74; 3,47</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,27</t>
+          <t>0,44; 2,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,55</t>
+          <t>3,82; 6,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,92</t>
+          <t>1,59; 3,89</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,17</t>
+          <t>0,86; 3,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,97; 7,91</t>
+          <t>4,92; 8,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,05</t>
+          <t>3,15; 5,08</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,54</t>
+          <t>3,71; 7,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 8,04</t>
+          <t>2,12; 8,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,01</t>
+          <t>2,66; 7,0</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,78</t>
+          <t>2,9; 6,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,91; 12,0</t>
+          <t>8,0; 12,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,45</t>
+          <t>6,48; 9,34</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,96</t>
+          <t>1,7; 2,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,98; 5,62</t>
+          <t>3,95; 5,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,16</t>
+          <t>3,14; 4,12</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses han visitado un podólogo</t>
+          <t>Población según si en los últimos 12 meses han visitado un podólogo (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1934; 21489</t>
+          <t>1921; 22329</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4126; 24021</t>
+          <t>4399; 23461</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8398; 33876</t>
+          <t>8986; 34548</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2394; 20237</t>
+          <t>2483; 19992</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4588; 19039</t>
+          <t>4233; 19450</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9237; 31939</t>
+          <t>8840; 29097</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5598; 20049</t>
+          <t>5790; 20700</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9934; 23116</t>
+          <t>9741; 22398</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18994; 37216</t>
+          <t>18765; 37399</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3179; 20135</t>
+          <t>3950; 20549</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27900; 46723</t>
+          <t>27213; 47107</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27533; 62814</t>
+          <t>25466; 62329</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4982; 17813</t>
+          <t>4852; 17457</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27210; 43300</t>
+          <t>26928; 43971</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34192; 56014</t>
+          <t>34968; 56318</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13941; 27749</t>
+          <t>13653; 27887</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10961; 48935</t>
+          <t>12906; 49047</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26725; 68436</t>
+          <t>25951; 68334</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8377; 19178</t>
+          <t>8195; 18601</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33641; 51030</t>
+          <t>34030; 51898</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>45541; 66878</t>
+          <t>45855; 66100</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>60157; 102574</t>
+          <t>58876; 98977</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>145653; 205827</t>
+          <t>144518; 207013</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>223998; 295999</t>
+          <t>223470; 293469</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1806_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1806_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 5,58</t>
+          <t>0,36; 4,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 7,49</t>
+          <t>1,12; 6,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,84</t>
+          <t>1,09; 4,36</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,72</t>
+          <t>0,5; 4,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,8</t>
+          <t>0,88; 3,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,11</t>
+          <t>0,97; 3,29</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,86</t>
+          <t>0,92; 3,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,13</t>
+          <t>1,68; 3,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,47</t>
+          <t>1,63; 3,16</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,31</t>
+          <t>0,8; 2,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,61</t>
+          <t>4,26; 6,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,89</t>
+          <t>2,86; 4,47</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,11</t>
+          <t>0,77; 2,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,04</t>
+          <t>4,88; 7,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,08</t>
+          <t>3,04; 4,88</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,57</t>
+          <t>3,59; 7,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 8,06</t>
+          <t>5,91; 9,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,0</t>
+          <t>5,23; 7,93</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,58</t>
+          <t>3,03; 6,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,0; 12,2</t>
+          <t>7,87; 11,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,48; 9,34</t>
+          <t>6,23; 9,19</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,86</t>
+          <t>1,84; 2,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,65</t>
+          <t>4,59; 5,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,12</t>
+          <t>3,4; 4,19</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>11028</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18148</t>
+          <t>17348</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1921; 22329</t>
+          <t>1488; 18541</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4399; 23461</t>
+          <t>4076; 24110</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8986; 34548</t>
+          <t>8373; 33568</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7583</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>18343</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2483; 19992</t>
+          <t>2404; 21034</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4233; 19450</t>
+          <t>4386; 19504</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8840; 29097</t>
+          <t>9438; 32178</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11496</t>
+          <t>11515</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15232</t>
+          <t>16935</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>28450</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5790; 20700</t>
+          <t>5714; 20344</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9741; 22398</t>
+          <t>10476; 24786</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18765; 37399</t>
+          <t>20204; 39292</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>11058</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>36444</t>
+          <t>40037</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47041</t>
+          <t>51095</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3950; 20549</t>
+          <t>5631; 20013</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27213; 47107</t>
+          <t>31405; 50640</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25466; 62329</t>
+          <t>41067; 64209</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>34591</t>
+          <t>37759</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>44340</t>
+          <t>47662</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4852; 17457</t>
+          <t>4712; 17549</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26928; 43971</t>
+          <t>29691; 47968</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34968; 56318</t>
+          <t>37051; 59360</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>21161</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>29713</t>
+          <t>32865</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49709</t>
+          <t>54026</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>13653; 27887</t>
+          <t>14626; 30117</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12906; 49047</t>
+          <t>25944; 42492</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25951; 68334</t>
+          <t>44230; 67144</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>12947</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>42242</t>
+          <t>45204</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>55189</t>
+          <t>59155</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8195; 18601</t>
+          <t>9385; 21434</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>34030; 51898</t>
+          <t>36538; 55329</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>45855; 66100</t>
+          <t>48259; 71144</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>79627</t>
+          <t>81942</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>179396</t>
+          <t>194137</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>259023</t>
+          <t>276079</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>58876; 98977</t>
+          <t>65067; 102269</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>144518; 207013</t>
+          <t>171546; 218572</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>223470; 293469</t>
+          <t>246892; 304186</t>
         </is>
       </c>
     </row>
